--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T20:00:37+00:00</t>
+    <t>2022-02-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-19T15:25:03+00:00</t>
+    <t>2022-05-23T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-23T06:59:28+00:00</t>
+    <t>2022-05-24T18:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-24T18:54:59+00:00</t>
+    <t>2022-08-17T21:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-17T21:15:17+00:00</t>
+    <t>2022-09-06T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T15:19:36+00:00</t>
+    <t>2022-09-06T18:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T18:47:55+00:00</t>
+    <t>2022-09-06T19:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:01:15+00:00</t>
+    <t>2022-09-06T19:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:02:52+00:00</t>
+    <t>2022-09-06T19:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:21:39+00:00</t>
+    <t>2022-09-13T07:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-13T07:22:16+00:00</t>
+    <t>2022-09-17T09:48:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:48:15+00:00</t>
+    <t>2022-09-17T09:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:59:31+00:00</t>
+    <t>2022-09-17T10:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T10:02:16+00:00</t>
+    <t>2022-10-04T11:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t>DK Request Status</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -369,125 +372,127 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
     </row>
@@ -503,114 +508,114 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -48,103 +48,103 @@
     <t>Status</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-04-18T12:02:45+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>draft</t>
   </si>
   <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2022-12-05T09:15:32+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Draft</t>
   </si>
   <si>
     <t>The request has been created but is not yet complete or ready for action.</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>Active</t>
@@ -525,13 +525,13 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -539,7 +539,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>44</v>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,61 +141,19 @@
     <t>draft</t>
   </si>
   <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>The request has been created but is not yet complete or ready for action.</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>The request is in force and ready to be acted upon.</t>
-  </si>
-  <si>
     <t>on-hold</t>
   </si>
   <si>
-    <t>On Hold</t>
-  </si>
-  <si>
-    <t>The request (and any implicit authorization to act) has been temporarily withdrawn but is expected to resume in the future.</t>
-  </si>
-  <si>
     <t>revoked</t>
   </si>
   <si>
-    <t>Revoked</t>
-  </si>
-  <si>
-    <t>The request (and any implicit authorization to act) has been terminated prior to the known full completion of the intended actions. No further activity should occur.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>The activity described by the request has been fully performed. No further activity will occur.</t>
-  </si>
-  <si>
     <t>entered-in-error</t>
   </si>
   <si>
-    <t>Entered in Error</t>
-  </si>
-  <si>
-    <t>This request should never have existed and should be considered 'void'. (It is possible that real-world decisions were based on it. If real-world activity has occurred, the status should be "revoked" rather than "entered-in-error".).</t>
-  </si>
-  <si>
     <t>unknown</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>The authoring system does not know which of the status values currently applies for this request.  Note: This concept is not to be used for "other"  - one of the listed statuses is presumed to apply, but the authoring/source system does not know which.</t>
   </si>
 </sst>
 </file>
@@ -527,12 +485,8 @@
       <c r="B2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>43</v>
-      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -541,82 +495,58 @@
       <c r="B3" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>45</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>51</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>54</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>60</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -48,112 +48,154 @@
     <t>Status</t>
   </si>
   <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-04-25T17:34:53+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>The request has been created but is not yet complete or ready for action.</t>
+  </si>
+  <si>
     <t>active</t>
   </si>
   <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-04-24T21:40:58+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>draft</t>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>The request is in force and ready to be acted upon.</t>
   </si>
   <si>
     <t>on-hold</t>
   </si>
   <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>The request (and any implicit authorization to act) has been temporarily withdrawn but is expected to resume in the future.</t>
+  </si>
+  <si>
     <t>revoked</t>
   </si>
   <si>
+    <t>Revoked</t>
+  </si>
+  <si>
+    <t>The request (and any implicit authorization to act) has been terminated prior to the known full completion of the intended actions. No further activity should occur.</t>
+  </si>
+  <si>
     <t>completed</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>The activity described by the request has been fully performed. No further activity will occur.</t>
+  </si>
+  <si>
     <t>entered-in-error</t>
   </si>
   <si>
+    <t>Entered in Error</t>
+  </si>
+  <si>
+    <t>This request should never have existed and should be considered 'void'. (It is possible that real-world decisions were based on it. If real-world activity has occurred, the status should be "revoked" rather than "entered-in-error".).</t>
+  </si>
+  <si>
     <t>unknown</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>The authoring system does not know which of the status values currently applies for this request.  Note: This concept is not to be used for "other"  - one of the listed statuses is presumed to apply, but the authoring/source system does not know which.</t>
   </si>
 </sst>
 </file>
@@ -483,70 +525,98 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -48,154 +48,112 @@
     <t>Status</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-04-30T20:59:20+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>draft</t>
   </si>
   <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-04-25T17:34:53+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>The request has been created but is not yet complete or ready for action.</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>The request is in force and ready to be acted upon.</t>
-  </si>
-  <si>
     <t>on-hold</t>
   </si>
   <si>
-    <t>On Hold</t>
-  </si>
-  <si>
-    <t>The request (and any implicit authorization to act) has been temporarily withdrawn but is expected to resume in the future.</t>
-  </si>
-  <si>
     <t>revoked</t>
   </si>
   <si>
-    <t>Revoked</t>
-  </si>
-  <si>
-    <t>The request (and any implicit authorization to act) has been terminated prior to the known full completion of the intended actions. No further activity should occur.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>The activity described by the request has been fully performed. No further activity will occur.</t>
-  </si>
-  <si>
     <t>entered-in-error</t>
   </si>
   <si>
-    <t>Entered in Error</t>
-  </si>
-  <si>
-    <t>This request should never have existed and should be considered 'void'. (It is possible that real-world decisions were based on it. If real-world activity has occurred, the status should be "revoked" rather than "entered-in-error".).</t>
-  </si>
-  <si>
     <t>unknown</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>The authoring system does not know which of the status values currently applies for this request.  Note: This concept is not to be used for "other"  - one of the listed statuses is presumed to apply, but the authoring/source system does not know which.</t>
   </si>
 </sst>
 </file>
@@ -525,98 +483,70 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>42</v>
-      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>45</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>51</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>54</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>60</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-11-28T12:13:03+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-05-05T00:02:52+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -275,10 +275,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-12-01T13:42:49+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>draft</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-12-01T12:31:40+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-01-08T22:02:06+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-01-06T18:57:36+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>No display for ContactDetail</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-05-06T06:35:09+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>draft</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-05-03T13:03:24+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-05-06T14:14:33+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-05-06T07:49:19+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-12-11T09:50:58+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>draft</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-12-11T08:38:49+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,97 +48,97 @@
     <t>Status</t>
   </si>
   <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-12-16T15:09:03+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Denmark</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Codes identifying the stage lifecycle stage of a request</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>Hierarchy</t>
+  </si>
+  <si>
+    <t>Compositional</t>
+  </si>
+  <si>
+    <t>Version Needed?</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>supplement</t>
+  </si>
+  <si>
+    <t>Supplements</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/request-status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-12-11T09:50:58+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Denmark</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Codes identifying the stage lifecycle stage of a request</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>Hierarchy</t>
-  </si>
-  <si>
-    <t>Compositional</t>
-  </si>
-  <si>
-    <t>Version Needed?</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>supplement</t>
-  </si>
-  <si>
-    <t>Supplements</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/request-status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>on-hold</t>
@@ -483,7 +483,7 @@
         <v>40</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-request-status-dk-supplement.xlsx
+++ b/CodeSystem-request-status-dk-supplement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
